--- a/KAMCHATKA_ZAPOLNENIE/07_ООО_Арма-Пром.xlsx
+++ b/KAMCHATKA_ZAPOLNENIE/07_ООО_Арма-Пром.xlsx
@@ -85,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -107,6 +107,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -485,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AE11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -598,7 +601,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Нацрежим ПП 1875 (ограничение): обязательны производитель, страна и ДЕЙСТВУЮЩИЙ номер реестровой записи ПП 719 (для ЕАЭС — евразийский реестр). Приложите выписку из ГИСП и сертификаты. Доставка — до Петропавловска-Камчатского (укажите вес).</t>
+          <t>Графы марка / производитель / страна / № записи частично ПРЕДЗАПОЛНЕНЫ нами по вашему КП и открытым данным — проверьте и исправьте, если не так.</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -632,238 +635,275 @@
       <c r="AD3" s="2" t="n"/>
       <c r="AE3" s="2" t="n"/>
     </row>
-    <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Нацрежим ПП 1875 (ограничение): обязательны производитель, страна и ДЕЙСТВУЮЩИЙ номер реестровой записи ПП 719 (для ЕАЭС — евразийский реестр). Приложите выписку из ГИСП и сертификаты. Доставка — до Петропавловска-Камчатского (укажите вес).</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="n"/>
+      <c r="U4" s="2" t="n"/>
+      <c r="V4" s="2" t="n"/>
+      <c r="W4" s="2" t="n"/>
+      <c r="X4" s="2" t="n"/>
+      <c r="Y4" s="2" t="n"/>
+      <c r="Z4" s="2" t="n"/>
+      <c r="AA4" s="2" t="n"/>
+      <c r="AB4" s="2" t="n"/>
+      <c r="AC4" s="2" t="n"/>
+      <c r="AD4" s="2" t="n"/>
+      <c r="AE4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="66" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Табл./№ ТЗ</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>ГОСТ/ТУ</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Ду, мм</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Проход</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Давление, МПа</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Температура, °С</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Среда</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Материал корпуса</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Климатическое исполнение</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Присоединение</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Приводное устройство: наименование</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Приводное устройство: технические характеристики</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Установочное положение</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Материал штока, шара, уплотнений</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Габариты</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>Ед.</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="U5" s="4" t="inlineStr">
         <is>
           <t>Предлагаемая марка / обозначение</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>Производитель (завод)</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t>Страна происхождения</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>№ реестровой записи (ПП 719) или евразийского реестра</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>Срок действия записи</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>Соответствие ТЗ: «да» или отличия</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>Цена за ед. с НДС, ₽</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr">
+      <c r="AB5" s="4" t="inlineStr">
         <is>
           <t>Сумма с НДС, ₽</t>
         </is>
       </c>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>Срок отгрузки</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AD5" s="4" t="inlineStr">
         <is>
           <t>Вес ед., кг / габариты</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>Сертификат / декларация ТР ТС №</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="5" t="n">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>1.3/2</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Клапан регулирующий 25ч945п Ду 15 Ру 16 с ЭИМ</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>ТУ 3722-011-50987615</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>стандарт</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>От -15°С до +150°С</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>вода</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>чугун СЧ20</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>У2</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>фланцевое</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>автоматический</t>
         </is>
       </c>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>электропривод</t>
         </is>
       </c>
-      <c r="O5" s="6" t="inlineStr">
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t>горизонтальное ЭИМ вверх</t>
         </is>
       </c>
-      <c r="P5" s="6" t="inlineStr">
+      <c r="P6" s="6" t="inlineStr">
         <is>
           <t>Корпус, крышка: СЧ20
 Плунжер, седло: Сталь 12Х13
@@ -871,147 +911,40 @@
 Уплотнение сальника:Фторопласт-4</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>строительная длинна 130мм</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>Пропускная способность — 4 м3</t>
         </is>
       </c>
-      <c r="S5" s="5" t="n">
+      <c r="S6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="T5" s="6" t="inlineStr">
+      <c r="T6" s="6" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="U5" s="7" t="n"/>
-      <c r="V5" s="7" t="n"/>
-      <c r="W5" s="7" t="n"/>
-      <c r="X5" s="7" t="n"/>
-      <c r="Y5" s="7" t="n"/>
-      <c r="Z5" s="7" t="n"/>
-      <c r="AA5" s="8" t="n"/>
-      <c r="AB5" s="9">
-        <f>AA5*S5</f>
-        <v/>
-      </c>
-      <c r="AC5" s="7" t="n"/>
-      <c r="AD5" s="7" t="n"/>
-      <c r="AE5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>1.3/3</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Клапан регулирующий 25ч945п Ду 25 Ру 16 с ЭИМ</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>ТУ 3722-011-50987615</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>стандарт</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>От -15°С до +150°С</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>вода</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>чугун СЧ20</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>У2</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>фланцевое</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>автоматический</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>электропривод</t>
-        </is>
-      </c>
-      <c r="O6" s="6" t="inlineStr">
-        <is>
-          <t>горизонтальное ЭИМ вверх</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>Корпус, крышка: СЧ20
-Плунжер, седло: Сталь 12Х13
-Уплотнение в затворе: Фторопласт-4
-Уплотнение сальника:Фторопласт-4</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>строительная длинна 160мм</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>Пропускная способность — 4 м3</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" s="6" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
       <c r="U6" s="7" t="n"/>
-      <c r="V6" s="7" t="n"/>
-      <c r="W6" s="7" t="n"/>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>ООО «Арма-Пром» (Старооскольский арматурный завод, ГК «Авангард», ТМ САЗ)</t>
+        </is>
+      </c>
+      <c r="W6" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
       <c r="X6" s="7" t="n"/>
       <c r="Y6" s="7" t="n"/>
       <c r="Z6" s="7" t="n"/>
-      <c r="AA6" s="8" t="n"/>
-      <c r="AB6" s="9">
+      <c r="AA6" s="9" t="n"/>
+      <c r="AB6" s="10">
         <f>AA6*S6</f>
         <v/>
       </c>
@@ -1021,16 +954,16 @@
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1.3/4</t>
+          <t>1.3/3</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Клапан регулирующий 25ч945п Ду 50 Ру 16 KV100 с ЭИМ</t>
+          <t>Клапан регулирующий 25ч945п Ду 25 Ру 16 с ЭИМ</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -1040,7 +973,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -1055,7 +988,7 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>От -20°С до +150°С</t>
+          <t>От -15°С до +150°С</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -1103,16 +1036,16 @@
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>строительная длинна 230мм</t>
+          <t>строительная длинна 160мм</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>Максимальная пропускная способность - 65 м3. Допустима 40 м3</t>
+          <t>Пропускная способность — 4 м3</t>
         </is>
       </c>
       <c r="S7" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
@@ -1120,13 +1053,21 @@
         </is>
       </c>
       <c r="U7" s="7" t="n"/>
-      <c r="V7" s="7" t="n"/>
-      <c r="W7" s="7" t="n"/>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>ООО «Арма-Пром» (Старооскольский арматурный завод, ГК «Авангард», ТМ САЗ)</t>
+        </is>
+      </c>
+      <c r="W7" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
       <c r="X7" s="7" t="n"/>
       <c r="Y7" s="7" t="n"/>
       <c r="Z7" s="7" t="n"/>
-      <c r="AA7" s="8" t="n"/>
-      <c r="AB7" s="9">
+      <c r="AA7" s="9" t="n"/>
+      <c r="AB7" s="10">
         <f>AA7*S7</f>
         <v/>
       </c>
@@ -1136,16 +1077,16 @@
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>1.3/5</t>
+          <t>1.3/4</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Клапан регулирующий 25ч945п Ду 80 Ру 16 с ЭИМ</t>
+          <t>Клапан регулирующий 25ч945п Ду 50 Ру 16 KV100 с ЭИМ</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1155,7 +1096,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -1170,7 +1111,7 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>От -15°С до +150°С</t>
+          <t>От -20°С до +150°С</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1218,16 +1159,16 @@
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>строительная длинна 160мм</t>
+          <t>строительная длинна 230мм</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>Пропускная способность — 4 м3</t>
+          <t>Максимальная пропускная способность - 65 м3. Допустима 40 м3</t>
         </is>
       </c>
       <c r="S8" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
@@ -1235,13 +1176,21 @@
         </is>
       </c>
       <c r="U8" s="7" t="n"/>
-      <c r="V8" s="7" t="n"/>
-      <c r="W8" s="7" t="n"/>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>ООО «Арма-Пром» (Старооскольский арматурный завод, ГК «Авангард», ТМ САЗ)</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
       <c r="X8" s="7" t="n"/>
       <c r="Y8" s="7" t="n"/>
       <c r="Z8" s="7" t="n"/>
-      <c r="AA8" s="8" t="n"/>
-      <c r="AB8" s="9">
+      <c r="AA8" s="9" t="n"/>
+      <c r="AB8" s="10">
         <f>AA8*S8</f>
         <v/>
       </c>
@@ -1251,47 +1200,98 @@
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>1.3/163</t>
+          <t>1.3/5</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Электропривод прямоходный Regada SТ0 490.0-00TQV/00</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
+          <t>Клапан регулирующий 25ч945п Ду 80 Ру 16 с ЭИМ</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>ТУ 3722-011-50987615</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>25°C - +55°C</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
+          <t>От -15°С до +150°С</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>вода</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>чугун СЧ20</t>
+        </is>
+      </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>У</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr"/>
-      <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="6" t="inlineStr"/>
-      <c r="O9" s="6" t="inlineStr"/>
-      <c r="P9" s="6" t="inlineStr"/>
-      <c r="Q9" s="6" t="inlineStr"/>
+          <t>У2</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>фланцевое</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>автоматический</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>электропривод</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>горизонтальное ЭИМ вверх</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>Корпус, крышка: СЧ20
+Плунжер, седло: Сталь 12Х13
+Уплотнение в затворе: Фторопласт-4
+Уплотнение сальника:Фторопласт-4</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>строительная длинна 160мм</t>
+        </is>
+      </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>Степень защиты IP 54, Питающее напряжение 230 V AC, Схема включения Z20, Выключающая сила 2 900 N, Макс. нагрузочная сила 2 500 N, Скорость управления 4 mm/min,  Электродвигатель 1 W, Выключение злектропривода от нагрузки Двухсиловое (Схема включения Z20 выключатели S1, S2), Рабочий ход с датчиком 25 mm, Датчик положения Электронный с R/I преобразователем с токовым сигналом С источником, Включение 2-проводник, Выход 4 - 20 mA, Схема включения Z269, Механическое присоединение Столбикы, Присоединительная высота 110мм, Прицоедин. резьба тяги M8x1-22, Эскиз P-1185/B, 2 добавочные выключатели положения, Схема включения Z21.</t>
+          <t>Пропускная способность — 4 м3</t>
         </is>
       </c>
       <c r="S9" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
@@ -1299,13 +1299,21 @@
         </is>
       </c>
       <c r="U9" s="7" t="n"/>
-      <c r="V9" s="7" t="n"/>
-      <c r="W9" s="7" t="n"/>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>ООО «Арма-Пром» (Старооскольский арматурный завод, ГК «Авангард», ТМ САЗ)</t>
+        </is>
+      </c>
+      <c r="W9" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
       <c r="X9" s="7" t="n"/>
       <c r="Y9" s="7" t="n"/>
       <c r="Z9" s="7" t="n"/>
-      <c r="AA9" s="8" t="n"/>
-      <c r="AB9" s="9">
+      <c r="AA9" s="9" t="n"/>
+      <c r="AB9" s="10">
         <f>AA9*S9</f>
         <v/>
       </c>
@@ -1314,44 +1322,116 @@
       <c r="AE9" s="7" t="n"/>
     </row>
     <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="10" t="inlineStr"/>
-      <c r="B10" s="10" t="inlineStr"/>
-      <c r="C10" s="10" t="inlineStr"/>
-      <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="10" t="inlineStr"/>
-      <c r="F10" s="10" t="inlineStr"/>
-      <c r="G10" s="10" t="inlineStr"/>
-      <c r="H10" s="10" t="inlineStr"/>
-      <c r="I10" s="10" t="inlineStr"/>
-      <c r="J10" s="10" t="inlineStr"/>
-      <c r="K10" s="10" t="inlineStr"/>
-      <c r="L10" s="10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr"/>
-      <c r="N10" s="10" t="inlineStr"/>
-      <c r="O10" s="10" t="inlineStr"/>
-      <c r="P10" s="10" t="inlineStr"/>
-      <c r="Q10" s="10" t="inlineStr"/>
-      <c r="R10" s="10" t="inlineStr"/>
-      <c r="S10" s="10" t="inlineStr"/>
-      <c r="T10" s="10" t="inlineStr"/>
-      <c r="U10" s="10" t="inlineStr"/>
-      <c r="V10" s="10" t="inlineStr"/>
-      <c r="W10" s="10" t="inlineStr"/>
-      <c r="X10" s="10" t="inlineStr"/>
-      <c r="Y10" s="10" t="inlineStr"/>
-      <c r="Z10" s="10" t="inlineStr"/>
-      <c r="AA10" s="10" t="inlineStr">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>1.3/163</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Электропривод прямоходный Regada SТ0 490.0-00TQV/00</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>25°C - +55°C</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr"/>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>У</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr"/>
+      <c r="M10" s="6" t="inlineStr"/>
+      <c r="N10" s="6" t="inlineStr"/>
+      <c r="O10" s="6" t="inlineStr"/>
+      <c r="P10" s="6" t="inlineStr"/>
+      <c r="Q10" s="6" t="inlineStr"/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Степень защиты IP 54, Питающее напряжение 230 V AC, Схема включения Z20, Выключающая сила 2 900 N, Макс. нагрузочная сила 2 500 N, Скорость управления 4 mm/min,  Электродвигатель 1 W, Выключение злектропривода от нагрузки Двухсиловое (Схема включения Z20 выключатели S1, S2), Рабочий ход с датчиком 25 mm, Датчик положения Электронный с R/I преобразователем с токовым сигналом С источником, Включение 2-проводник, Выход 4 - 20 mA, Схема включения Z269, Механическое присоединение Столбикы, Присоединительная высота 110мм, Прицоедин. резьба тяги M8x1-22, Эскиз P-1185/B, 2 добавочные выключатели положения, Схема включения Z21.</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="U10" s="7" t="n"/>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>ООО «Арма-Пром» (Старооскольский арматурный завод, ГК «Авангард», ТМ САЗ)</t>
+        </is>
+      </c>
+      <c r="W10" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X10" s="7" t="n"/>
+      <c r="Y10" s="7" t="n"/>
+      <c r="Z10" s="7" t="n"/>
+      <c r="AA10" s="9" t="n"/>
+      <c r="AB10" s="10">
+        <f>AA10*S10</f>
+        <v/>
+      </c>
+      <c r="AC10" s="7" t="n"/>
+      <c r="AD10" s="7" t="n"/>
+      <c r="AE10" s="7" t="n"/>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="11" t="inlineStr"/>
+      <c r="B11" s="11" t="inlineStr"/>
+      <c r="C11" s="11" t="inlineStr"/>
+      <c r="D11" s="11" t="inlineStr"/>
+      <c r="E11" s="11" t="inlineStr"/>
+      <c r="F11" s="11" t="inlineStr"/>
+      <c r="G11" s="11" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr"/>
+      <c r="I11" s="11" t="inlineStr"/>
+      <c r="J11" s="11" t="inlineStr"/>
+      <c r="K11" s="11" t="inlineStr"/>
+      <c r="L11" s="11" t="inlineStr"/>
+      <c r="M11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr"/>
+      <c r="O11" s="11" t="inlineStr"/>
+      <c r="P11" s="11" t="inlineStr"/>
+      <c r="Q11" s="11" t="inlineStr"/>
+      <c r="R11" s="11" t="inlineStr"/>
+      <c r="S11" s="11" t="inlineStr"/>
+      <c r="T11" s="11" t="inlineStr"/>
+      <c r="U11" s="11" t="inlineStr"/>
+      <c r="V11" s="11" t="inlineStr"/>
+      <c r="W11" s="11" t="inlineStr"/>
+      <c r="X11" s="11" t="inlineStr"/>
+      <c r="Y11" s="11" t="inlineStr"/>
+      <c r="Z11" s="11" t="inlineStr"/>
+      <c r="AA11" s="11" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="AB10" s="11">
-        <f>SUM(AB5:AB9)</f>
+      <c r="AB11" s="12">
+        <f>SUM(AB6:AB10)</f>
         <v/>
       </c>
-      <c r="AC10" s="2" t="n"/>
-      <c r="AD10" s="2" t="n"/>
-      <c r="AE10" s="2" t="n"/>
+      <c r="AC11" s="2" t="n"/>
+      <c r="AD11" s="2" t="n"/>
+      <c r="AE11" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
